--- a/Hitster_BE.xlsx
+++ b/Hitster_BE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kuleuven-my.sharepoint.com/personal/jakob_depeuter_student_kuleuven_be/Documents/Documents/GitHub/hitster-be/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{CA620351-37C9-493E-AD22-44F3F236D7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD541156-B70B-4CF8-BEA7-F4F62B81545F}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{CA620351-37C9-493E-AD22-44F3F236D7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99431278-B259-4426-B6E3-C355B2425A70}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{7D5BECDE-3070-4858-9EF0-6742C2B48E55}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7D5BECDE-3070-4858-9EF0-6742C2B48E55}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -1613,9 +1613,6 @@
     <t>The Beatles</t>
   </si>
   <si>
-    <t>spotify:track:40XeGNGFchGYw7y0ue1GiG</t>
-  </si>
-  <si>
     <t>Stromae</t>
   </si>
   <si>
@@ -1926,6 +1923,9 @@
   </si>
   <si>
     <t>https://open.spotify.com/track/3qhlB30KknSejmIvZZLjOD?si=e50747bda4a8401b</t>
+  </si>
+  <si>
+    <t>https://open.spotify.com/track/5ZBeML7Lf3FMEVviTyvi8l?si=9671a370a0e944fa</t>
   </si>
 </sst>
 </file>
@@ -2364,16 +2364,16 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>564</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>565</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>566</v>
       </c>
       <c r="C4">
         <v>2018</v>
       </c>
       <c r="D4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -2476,16 +2476,16 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>527</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>529</v>
       </c>
       <c r="C12">
         <v>1983</v>
       </c>
       <c r="D12" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -2787,7 +2787,7 @@
         <v>167</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C34">
         <v>1980</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>524</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>526</v>
       </c>
       <c r="C39">
         <v>2022</v>
       </c>
       <c r="D39" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -2969,7 +2969,7 @@
         <v>48</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C47">
         <v>1986</v>
@@ -2997,7 +2997,7 @@
         <v>195</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C49">
         <v>1983</v>
@@ -3008,16 +3008,16 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C50">
         <v>2008</v>
       </c>
       <c r="D50" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -3036,7 +3036,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>336</v>
@@ -3064,16 +3064,16 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>542</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>543</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>544</v>
       </c>
       <c r="C54">
         <v>1964</v>
       </c>
       <c r="D54" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -3106,16 +3106,16 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>547</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>549</v>
       </c>
       <c r="C57">
         <v>2001</v>
       </c>
       <c r="D57" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -3274,16 +3274,16 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>530</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>531</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>532</v>
       </c>
       <c r="C69">
         <v>1954</v>
       </c>
       <c r="D69" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -3386,16 +3386,16 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>533</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>534</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>535</v>
       </c>
       <c r="C77">
         <v>2025</v>
       </c>
       <c r="D77" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -3543,7 +3543,7 @@
         <v>209</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C88">
         <v>1985</v>
@@ -3680,16 +3680,16 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C98">
         <v>2011</v>
       </c>
       <c r="D98" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
@@ -3725,13 +3725,13 @@
         <v>436</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C101">
         <v>1950</v>
       </c>
       <c r="D101" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
@@ -3781,13 +3781,13 @@
         <v>523</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C105">
         <v>1963</v>
       </c>
-      <c r="D105" t="s">
-        <v>524</v>
+      <c r="D105" s="2" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
@@ -3949,7 +3949,7 @@
         <v>262</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C117">
         <v>1983</v>
@@ -4100,16 +4100,16 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C128">
         <v>1965</v>
       </c>
       <c r="D128" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
@@ -4198,16 +4198,16 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
+        <v>558</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>559</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>560</v>
       </c>
       <c r="C135">
         <v>2002</v>
       </c>
       <c r="D135" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
@@ -4285,7 +4285,7 @@
         <v>163</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C141">
         <v>1978</v>
@@ -4383,7 +4383,7 @@
         <v>521</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C148">
         <v>1991</v>
@@ -4534,16 +4534,16 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
+        <v>536</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>538</v>
       </c>
       <c r="C159">
         <v>2024</v>
       </c>
       <c r="D159" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
@@ -4579,7 +4579,7 @@
         <v>25</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C162">
         <v>1978</v>
@@ -4646,30 +4646,30 @@
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
+        <v>539</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>540</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>541</v>
       </c>
       <c r="C167">
         <v>2023</v>
       </c>
       <c r="D167" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C168">
         <v>2011</v>
       </c>
       <c r="D168" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
@@ -4831,7 +4831,7 @@
         <v>143</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C180">
         <v>1975</v>
@@ -4982,16 +4982,16 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C191">
         <v>1970</v>
       </c>
       <c r="D191" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
@@ -5024,16 +5024,16 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
+        <v>561</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>562</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>563</v>
       </c>
       <c r="C194">
         <v>2009</v>
       </c>
       <c r="D194" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
@@ -5041,7 +5041,7 @@
         <v>165</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C195">
         <v>1979</v>
@@ -5061,203 +5061,203 @@
         <v>2008</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
+        <v>575</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>576</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>577</v>
       </c>
       <c r="C197">
         <v>2013</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
+        <v>579</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>580</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>581</v>
       </c>
       <c r="C198">
         <v>2014</v>
       </c>
       <c r="D198" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
+        <v>581</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>582</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>583</v>
       </c>
       <c r="C199">
         <v>2014</v>
       </c>
       <c r="D199" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
+        <v>583</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>584</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>585</v>
       </c>
       <c r="C200">
         <v>2015</v>
       </c>
       <c r="D200" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
+        <v>585</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>586</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>587</v>
       </c>
       <c r="C201">
         <v>2015</v>
       </c>
       <c r="D201" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
+        <v>587</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>588</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>589</v>
       </c>
       <c r="C202">
         <v>2015</v>
       </c>
       <c r="D202" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
+        <v>589</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>590</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>591</v>
       </c>
       <c r="C203">
         <v>2016</v>
       </c>
       <c r="D203" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
+        <v>591</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>592</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>593</v>
       </c>
       <c r="C204">
         <v>2016</v>
       </c>
       <c r="D204" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
+        <v>577</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>578</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>579</v>
       </c>
       <c r="C205">
         <v>2017</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C206">
         <v>2019</v>
       </c>
       <c r="D206" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
+        <v>573</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>574</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>575</v>
       </c>
       <c r="C207">
         <v>2022</v>
       </c>
       <c r="D207" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
+        <v>569</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>570</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>571</v>
       </c>
       <c r="C208">
         <v>2024</v>
       </c>
       <c r="D208" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
+        <v>571</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>572</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>573</v>
       </c>
       <c r="C209">
         <v>2025</v>
       </c>
       <c r="D209" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C210">
         <v>2022</v>
       </c>
       <c r="D210" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
   </sheetData>
@@ -5270,6 +5270,7 @@
     <hyperlink ref="D196" r:id="rId1" display="https://open.spotify.com/track/6TfBA04WJ3X1d1wXhaCFVT?si=256b761b9b36429b" xr:uid="{0496E95B-E7C8-42CF-AD44-FA16D389EFDF}"/>
     <hyperlink ref="D197" r:id="rId2" xr:uid="{B506D318-9113-4D07-A4C6-B50CDACD7993}"/>
     <hyperlink ref="D205" r:id="rId3" xr:uid="{126F7FBE-D80C-4D98-A183-26D320DEFF60}"/>
+    <hyperlink ref="D105" r:id="rId4" xr:uid="{EAB6043C-7E05-4C88-AD8F-F1C26B8FC802}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Hitster_BE.xlsx
+++ b/Hitster_BE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kuleuven-my.sharepoint.com/personal/jakob_depeuter_student_kuleuven_be/Documents/Documents/GitHub/hitster-be/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="102" documentId="8_{CA620351-37C9-493E-AD22-44F3F236D7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66D3F8B1-3435-455C-8BB3-470AC21B4A39}"/>
+  <xr:revisionPtr revIDLastSave="109" documentId="8_{CA620351-37C9-493E-AD22-44F3F236D7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F86E0805-7CBF-4BF0-BC4C-8DBC15FFBC27}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{7D5BECDE-3070-4858-9EF0-6742C2B48E55}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7D5BECDE-3070-4858-9EF0-6742C2B48E55}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -1889,9 +1889,6 @@
     <t>Wheels of Steel</t>
   </si>
   <si>
-    <t>Blue Ã–yster Cult</t>
-  </si>
-  <si>
     <t>California Dreamin'</t>
   </si>
   <si>
@@ -1901,27 +1898,9 @@
     <t>You're Gonna Go Far, Kid</t>
   </si>
   <si>
-    <t>EmilÃ­ana Torrini</t>
-  </si>
-  <si>
     <t>Without You</t>
   </si>
   <si>
-    <t>MÃ¶tley CrÃ¼e</t>
-  </si>
-  <si>
-    <t>Lâ€™enfer</t>
-  </si>
-  <si>
-    <t>LaÃ¯s</t>
-  </si>
-  <si>
-    <t>AngÃ¨le</t>
-  </si>
-  <si>
-    <t>Eviva EspaÃ±a</t>
-  </si>
-  <si>
     <t>Twist And Shout</t>
   </si>
   <si>
@@ -2406,6 +2385,27 @@
   </si>
   <si>
     <t>spotify:track:42og107RMzQPsQUIJBSUbD</t>
+  </si>
+  <si>
+    <t>Mötley Crüe</t>
+  </si>
+  <si>
+    <t>Laïs</t>
+  </si>
+  <si>
+    <t>Angèle</t>
+  </si>
+  <si>
+    <t>L'enfer</t>
+  </si>
+  <si>
+    <t>Blue Öyster Cult</t>
+  </si>
+  <si>
+    <t>Emili­ana Torrini</t>
+  </si>
+  <si>
+    <t>Eviva Espana</t>
   </si>
 </sst>
 </file>
@@ -3683,7 +3683,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>616</v>
+        <v>786</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>16</v>
@@ -3798,7 +3798,7 @@
         <v>538</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C72" s="1">
         <v>1965</v>
@@ -3851,7 +3851,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>332</v>
@@ -4134,7 +4134,7 @@
         <v>394</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C96" s="1">
         <v>2008</v>
@@ -4635,7 +4635,7 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
-        <v>620</v>
+        <v>787</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>398</v>
@@ -4666,7 +4666,7 @@
         <v>548</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C134" s="1">
         <v>2011</v>
@@ -4761,7 +4761,7 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>622</v>
+        <v>782</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>197</v>
@@ -4820,7 +4820,7 @@
         <v>518</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>623</v>
+        <v>785</v>
       </c>
       <c r="C145" s="1">
         <v>2022</v>
@@ -4845,7 +4845,7 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>624</v>
+        <v>783</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>76</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
-        <v>625</v>
+        <v>784</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>556</v>
@@ -5478,7 +5478,7 @@
         <v>123</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>626</v>
+        <v>788</v>
       </c>
       <c r="C192" s="1">
         <v>1971</v>
@@ -5520,13 +5520,13 @@
         <v>517</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="C195" s="1">
         <v>1963</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
@@ -5540,7 +5540,7 @@
         <v>1970</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
@@ -5554,7 +5554,7 @@
         <v>2024</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
@@ -5562,13 +5562,13 @@
         <v>561</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="C198" s="1">
         <v>2022</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
@@ -5582,7 +5582,7 @@
         <v>2022</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
@@ -5596,7 +5596,7 @@
         <v>2013</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
@@ -5610,7 +5610,7 @@
         <v>2017</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
@@ -5624,7 +5624,7 @@
         <v>2013</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
@@ -5638,7 +5638,7 @@
         <v>2014</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
@@ -5652,7 +5652,7 @@
         <v>2015</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
@@ -5666,7 +5666,7 @@
         <v>2015</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
@@ -5680,7 +5680,7 @@
         <v>2015</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
@@ -5694,7 +5694,7 @@
         <v>2016</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
@@ -5708,7 +5708,7 @@
         <v>2016</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
@@ -5722,7 +5722,7 @@
         <v>2019</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
@@ -5736,7 +5736,7 @@
         <v>2022</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
@@ -5750,7 +5750,7 @@
         <v>2015</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
@@ -5764,7 +5764,7 @@
         <v>2024</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
@@ -5778,7 +5778,7 @@
         <v>2014</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
@@ -5792,7 +5792,7 @@
         <v>1984</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.3">
@@ -5806,7 +5806,7 @@
         <v>1984</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.3">
@@ -5820,7 +5820,7 @@
         <v>1981</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
@@ -5834,7 +5834,7 @@
         <v>1981</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -5848,7 +5848,7 @@
         <v>1978</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.3">
@@ -5862,7 +5862,7 @@
         <v>1984</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
@@ -5876,54 +5876,54 @@
         <v>1981</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="C221" s="1">
         <v>2004</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="C222" s="1">
         <v>2004</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="C223" s="1">
         <v>2004</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>465</v>
@@ -5932,581 +5932,581 @@
         <v>2003</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="C225" s="1">
         <v>2003</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="C226" s="1">
         <v>1999</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="C227" s="1">
         <v>1999</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="C228" s="1">
         <v>1998</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="C229" s="1">
         <v>1997</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="C230" s="1">
         <v>1997</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="C231" s="1">
         <v>1995</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="C232" s="1">
         <v>1995</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="C233" s="1">
         <v>1995</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="C234" s="1">
         <v>1995</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="C235" s="1">
         <v>1994</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="C236" s="1">
         <v>1994</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="C237" s="1">
         <v>1992</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="C238" s="1">
         <v>1992</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="C239" s="1">
         <v>1992</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="C240" s="1">
         <v>1991</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="C241" s="1">
         <v>1941</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="C242" s="1">
         <v>1949</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="C243" s="1">
         <v>1942</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" s="3" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="C244" s="1">
         <v>1952</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="C245" s="1">
         <v>1951</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="C246" s="1">
         <v>1952</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="C247" s="1">
         <v>1953</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" s="3" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="C248" s="1">
         <v>1958</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="C249" s="1">
         <v>2006</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A250" s="3" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="C250" s="1">
         <v>2017</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="C251" s="1">
         <v>2018</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" s="3" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="C252" s="1">
         <v>2018</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="C253" s="1">
         <v>2019</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" s="3" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="C254" s="1">
         <v>2020</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="C255" s="1">
         <v>2021</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256" s="3" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="C256" s="1">
         <v>1961</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="C257" s="1">
         <v>1961</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" s="3" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="C258" s="1">
         <v>1964</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="C259" s="1">
         <v>1964</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A260" s="3" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="C260" s="1">
         <v>1967</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="C261" s="1">
         <v>1967</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A262" s="3" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="C262" s="1">
         <v>1967</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="C263" s="1">
         <v>1948</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A264" s="3" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="C264" s="1">
         <v>1946</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="C265" s="1">
         <v>1944</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
     </row>
   </sheetData>
